--- a/output/yearly_population_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_44_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5600</v>
+        <v>7125</v>
       </c>
       <c r="C2" t="n">
-        <v>7421</v>
+        <v>7058</v>
       </c>
       <c r="D2" t="n">
-        <v>23021</v>
+        <v>19635</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2914</v>
+        <v>4158</v>
       </c>
       <c r="C3" t="n">
-        <v>6100</v>
+        <v>6350</v>
       </c>
       <c r="D3" t="n">
-        <v>13760</v>
+        <v>15482</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2258</v>
+        <v>3118</v>
       </c>
       <c r="C4" t="n">
-        <v>5036</v>
+        <v>5613</v>
       </c>
       <c r="D4" t="n">
-        <v>7437</v>
+        <v>8640</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1508</v>
+        <v>2102</v>
       </c>
       <c r="C5" t="n">
-        <v>4643</v>
+        <v>4651</v>
       </c>
       <c r="D5" t="n">
-        <v>2956</v>
+        <v>3360</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>1177</v>
       </c>
       <c r="C6" t="n">
-        <v>3410</v>
+        <v>2876</v>
       </c>
       <c r="D6" t="n">
-        <v>1199</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>549</v>
       </c>
       <c r="C7" t="n">
-        <v>2141</v>
+        <v>1741</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="C8" t="n">
-        <v>1017</v>
+        <v>887</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>415</v>
+        <v>380</v>
       </c>
       <c r="D9" t="n">
         <v>306</v>
@@ -895,7 +895,7 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5427</v>
+        <v>7476</v>
       </c>
       <c r="C2" t="n">
-        <v>10324</v>
+        <v>5454</v>
       </c>
       <c r="D2" t="n">
-        <v>32826</v>
+        <v>16424</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3301</v>
+        <v>4462</v>
       </c>
       <c r="C3" t="n">
-        <v>5895</v>
+        <v>5875</v>
       </c>
       <c r="D3" t="n">
-        <v>14094</v>
+        <v>15006</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2172</v>
+        <v>3037</v>
       </c>
       <c r="C4" t="n">
-        <v>5383</v>
+        <v>5842</v>
       </c>
       <c r="D4" t="n">
-        <v>8242</v>
+        <v>9493</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1633</v>
+        <v>2240</v>
       </c>
       <c r="C5" t="n">
-        <v>4727</v>
+        <v>4943</v>
       </c>
       <c r="D5" t="n">
-        <v>3526</v>
+        <v>4036</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1053</v>
+        <v>1423</v>
       </c>
       <c r="C6" t="n">
-        <v>3888</v>
+        <v>3632</v>
       </c>
       <c r="D6" t="n">
-        <v>1452</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>732</v>
       </c>
       <c r="C7" t="n">
-        <v>2699</v>
+        <v>2212</v>
       </c>
       <c r="D7" t="n">
-        <v>726</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="C8" t="n">
-        <v>1480</v>
+        <v>1246</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>579</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7529</v>
+        <v>8653</v>
       </c>
       <c r="C2" t="n">
-        <v>8013</v>
+        <v>5336</v>
       </c>
       <c r="D2" t="n">
-        <v>30516</v>
+        <v>21174</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3378</v>
+        <v>4607</v>
       </c>
       <c r="C3" t="n">
-        <v>6829</v>
+        <v>5121</v>
       </c>
       <c r="D3" t="n">
-        <v>15439</v>
+        <v>14215</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2224</v>
+        <v>3062</v>
       </c>
       <c r="C4" t="n">
-        <v>5440</v>
+        <v>5678</v>
       </c>
       <c r="D4" t="n">
-        <v>8755</v>
+        <v>9907</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1646</v>
+        <v>2276</v>
       </c>
       <c r="C5" t="n">
-        <v>4905</v>
+        <v>5163</v>
       </c>
       <c r="D5" t="n">
-        <v>4097</v>
+        <v>4699</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1170</v>
+        <v>1592</v>
       </c>
       <c r="C6" t="n">
-        <v>4153</v>
+        <v>4128</v>
       </c>
       <c r="D6" t="n">
-        <v>1697</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>681</v>
+        <v>906</v>
       </c>
       <c r="C7" t="n">
-        <v>3175</v>
+        <v>2746</v>
       </c>
       <c r="D7" t="n">
-        <v>818</v>
+        <v>875</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>329</v>
+        <v>408</v>
       </c>
       <c r="C8" t="n">
-        <v>1930</v>
+        <v>1602</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="C9" t="n">
-        <v>959</v>
+        <v>827</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>427</v>
+        <v>381</v>
       </c>
       <c r="D10" t="n">
         <v>252</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
         <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6778</v>
+        <v>7952</v>
       </c>
       <c r="C2" t="n">
-        <v>5512</v>
+        <v>3671</v>
       </c>
       <c r="D2" t="n">
-        <v>25153</v>
+        <v>17621</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4024</v>
+        <v>5513</v>
       </c>
       <c r="C3" t="n">
-        <v>9698</v>
+        <v>7857</v>
       </c>
       <c r="D3" t="n">
-        <v>16769</v>
+        <v>16007</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1520</v>
+        <v>2103</v>
       </c>
       <c r="C4" t="n">
-        <v>7685</v>
+        <v>8063</v>
       </c>
       <c r="D4" t="n">
-        <v>8547</v>
+        <v>9715</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1081</v>
+        <v>1471</v>
       </c>
       <c r="C5" t="n">
-        <v>4069</v>
+        <v>4045</v>
       </c>
       <c r="D5" t="n">
-        <v>2764</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>629</v>
+        <v>837</v>
       </c>
       <c r="C6" t="n">
-        <v>3111</v>
+        <v>2691</v>
       </c>
       <c r="D6" t="n">
-        <v>801</v>
+        <v>857</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>303</v>
+        <v>376</v>
       </c>
       <c r="C7" t="n">
-        <v>1891</v>
+        <v>1569</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>939</v>
+        <v>810</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>418</v>
+        <v>373</v>
       </c>
       <c r="D9" t="n">
         <v>246</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4018</v>
+        <v>4930</v>
       </c>
       <c r="C2" t="n">
-        <v>3573</v>
+        <v>1902</v>
       </c>
       <c r="D2" t="n">
-        <v>18739</v>
+        <v>12155</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4431</v>
+        <v>5644</v>
       </c>
       <c r="C3" t="n">
-        <v>7090</v>
+        <v>5419</v>
       </c>
       <c r="D3" t="n">
-        <v>17104</v>
+        <v>15458</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2136</v>
+        <v>2940</v>
       </c>
       <c r="C4" t="n">
-        <v>8747</v>
+        <v>8032</v>
       </c>
       <c r="D4" t="n">
-        <v>9553</v>
+        <v>10418</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1192</v>
+        <v>1630</v>
       </c>
       <c r="C5" t="n">
-        <v>5598</v>
+        <v>5813</v>
       </c>
       <c r="D5" t="n">
-        <v>3454</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>744</v>
+        <v>988</v>
       </c>
       <c r="C6" t="n">
-        <v>3631</v>
+        <v>3323</v>
       </c>
       <c r="D6" t="n">
-        <v>1003</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>354</v>
       </c>
       <c r="C7" t="n">
-        <v>2361</v>
+        <v>1988</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>1240</v>
+        <v>1060</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>463</v>
+        <v>416</v>
       </c>
       <c r="D9" t="n">
         <v>255</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3557</v>
+        <v>5891</v>
       </c>
       <c r="C2" t="n">
-        <v>9615</v>
+        <v>2872</v>
       </c>
       <c r="D2" t="n">
-        <v>16616</v>
+        <v>11272</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3577</v>
+        <v>4533</v>
       </c>
       <c r="C3" t="n">
-        <v>4792</v>
+        <v>3340</v>
       </c>
       <c r="D3" t="n">
-        <v>16176</v>
+        <v>13970</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>3499</v>
       </c>
       <c r="C4" t="n">
-        <v>7753</v>
+        <v>6585</v>
       </c>
       <c r="D4" t="n">
-        <v>10494</v>
+        <v>10923</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1396</v>
+        <v>1940</v>
       </c>
       <c r="C5" t="n">
-        <v>7016</v>
+        <v>6735</v>
       </c>
       <c r="D5" t="n">
-        <v>4285</v>
+        <v>4804</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>863</v>
+        <v>1162</v>
       </c>
       <c r="C6" t="n">
-        <v>4464</v>
+        <v>4446</v>
       </c>
       <c r="D6" t="n">
-        <v>1342</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>408</v>
+        <v>524</v>
       </c>
       <c r="C7" t="n">
-        <v>2930</v>
+        <v>2582</v>
       </c>
       <c r="D7" t="n">
-        <v>583</v>
+        <v>602</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="C8" t="n">
-        <v>1702</v>
+        <v>1442</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>756</v>
+        <v>659</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2101</v>
+        <v>3499</v>
       </c>
       <c r="C2" t="n">
-        <v>4494</v>
+        <v>1359</v>
       </c>
       <c r="D2" t="n">
-        <v>11593</v>
+        <v>7885</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3476</v>
+        <v>4688</v>
       </c>
       <c r="C3" t="n">
-        <v>6266</v>
+        <v>3081</v>
       </c>
       <c r="D3" t="n">
-        <v>15859</v>
+        <v>13376</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2934</v>
+        <v>3880</v>
       </c>
       <c r="C4" t="n">
-        <v>7369</v>
+        <v>6021</v>
       </c>
       <c r="D4" t="n">
-        <v>11210</v>
+        <v>11424</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1478</v>
+        <v>2035</v>
       </c>
       <c r="C5" t="n">
-        <v>8298</v>
+        <v>7686</v>
       </c>
       <c r="D5" t="n">
-        <v>4519</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>727</v>
+        <v>956</v>
       </c>
       <c r="C6" t="n">
-        <v>5396</v>
+        <v>5336</v>
       </c>
       <c r="D6" t="n">
-        <v>1313</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>3074</v>
+        <v>2695</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1257</v>
+        <v>1083</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2143</v>
+        <v>4729</v>
       </c>
       <c r="C2" t="n">
-        <v>5358</v>
+        <v>6719</v>
       </c>
       <c r="D2" t="n">
-        <v>12800</v>
+        <v>10359</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2495</v>
+        <v>3572</v>
       </c>
       <c r="C3" t="n">
-        <v>4865</v>
+        <v>2033</v>
       </c>
       <c r="D3" t="n">
-        <v>14365</v>
+        <v>11730</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>3713</v>
       </c>
       <c r="C4" t="n">
-        <v>6767</v>
+        <v>4542</v>
       </c>
       <c r="D4" t="n">
-        <v>11583</v>
+        <v>11395</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1817</v>
+        <v>2468</v>
       </c>
       <c r="C5" t="n">
-        <v>7715</v>
+        <v>6848</v>
       </c>
       <c r="D5" t="n">
-        <v>5345</v>
+        <v>5915</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>913</v>
+        <v>1246</v>
       </c>
       <c r="C6" t="n">
-        <v>6677</v>
+        <v>6331</v>
       </c>
       <c r="D6" t="n">
-        <v>1726</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>355</v>
       </c>
       <c r="C7" t="n">
-        <v>4013</v>
+        <v>3807</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1939</v>
+        <v>1688</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>623</v>
+        <v>553</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3131,7 +3131,7 @@
         <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1505</v>
+        <v>3375</v>
       </c>
       <c r="C2" t="n">
-        <v>4038</v>
+        <v>4069</v>
       </c>
       <c r="D2" t="n">
-        <v>9368</v>
+        <v>8667</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2088</v>
+        <v>3461</v>
       </c>
       <c r="C3" t="n">
-        <v>4594</v>
+        <v>3585</v>
       </c>
       <c r="D3" t="n">
-        <v>13395</v>
+        <v>10927</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2484</v>
+        <v>3379</v>
       </c>
       <c r="C4" t="n">
-        <v>6054</v>
+        <v>3542</v>
       </c>
       <c r="D4" t="n">
-        <v>11827</v>
+        <v>11203</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1981</v>
+        <v>2711</v>
       </c>
       <c r="C5" t="n">
-        <v>7439</v>
+        <v>6061</v>
       </c>
       <c r="D5" t="n">
-        <v>5892</v>
+        <v>6480</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1082</v>
+        <v>1459</v>
       </c>
       <c r="C6" t="n">
-        <v>7277</v>
+        <v>6760</v>
       </c>
       <c r="D6" t="n">
-        <v>2068</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>252</v>
+        <v>334</v>
       </c>
       <c r="C7" t="n">
-        <v>4939</v>
+        <v>4709</v>
       </c>
       <c r="D7" t="n">
-        <v>749</v>
+        <v>802</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>2483</v>
+        <v>2227</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>704</v>
+        <v>647</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3599</v>
+        <v>4404</v>
       </c>
       <c r="C2" t="n">
-        <v>15583</v>
+        <v>8227</v>
       </c>
       <c r="D2" t="n">
-        <v>13690</v>
+        <v>10626</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1584</v>
+        <v>2883</v>
       </c>
       <c r="C3" t="n">
-        <v>3891</v>
+        <v>3390</v>
       </c>
       <c r="D3" t="n">
-        <v>12054</v>
+        <v>9956</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2058</v>
+        <v>2991</v>
       </c>
       <c r="C4" t="n">
-        <v>5311</v>
+        <v>3486</v>
       </c>
       <c r="D4" t="n">
-        <v>11693</v>
+        <v>10822</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1961</v>
+        <v>2682</v>
       </c>
       <c r="C5" t="n">
-        <v>6725</v>
+        <v>4895</v>
       </c>
       <c r="D5" t="n">
-        <v>6510</v>
+        <v>6855</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1287</v>
+        <v>1758</v>
       </c>
       <c r="C6" t="n">
-        <v>7278</v>
+        <v>6426</v>
       </c>
       <c r="D6" t="n">
-        <v>2518</v>
+        <v>2802</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>454</v>
+        <v>619</v>
       </c>
       <c r="C7" t="n">
-        <v>5856</v>
+        <v>5491</v>
       </c>
       <c r="D7" t="n">
-        <v>896</v>
+        <v>980</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>3324</v>
+        <v>3147</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1285</v>
+        <v>1179</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
         <v>138</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5403</v>
+        <v>6603</v>
       </c>
       <c r="C2" t="n">
-        <v>9376</v>
+        <v>8032</v>
       </c>
       <c r="D2" t="n">
-        <v>5016</v>
+        <v>19036</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2599</v>
+        <v>3118</v>
       </c>
       <c r="C2" t="n">
-        <v>8975</v>
+        <v>4607</v>
       </c>
       <c r="D2" t="n">
-        <v>10185</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2303</v>
+        <v>3821</v>
       </c>
       <c r="C3" t="n">
-        <v>6852</v>
+        <v>4838</v>
       </c>
       <c r="D3" t="n">
-        <v>13124</v>
+        <v>10965</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2862</v>
+        <v>3984</v>
       </c>
       <c r="C4" t="n">
-        <v>7602</v>
+        <v>5193</v>
       </c>
       <c r="D4" t="n">
-        <v>12001</v>
+        <v>11241</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1225</v>
+        <v>1723</v>
       </c>
       <c r="C5" t="n">
-        <v>10102</v>
+        <v>8217</v>
       </c>
       <c r="D5" t="n">
-        <v>5921</v>
+        <v>6374</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>419</v>
+        <v>571</v>
       </c>
       <c r="C6" t="n">
-        <v>7094</v>
+        <v>6703</v>
       </c>
       <c r="D6" t="n">
-        <v>1997</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>3257</v>
+        <v>3084</v>
       </c>
       <c r="D7" t="n">
-        <v>544</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1259</v>
+        <v>1155</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>135</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5918</v>
+        <v>8214</v>
       </c>
       <c r="C2" t="n">
-        <v>6381</v>
+        <v>6068</v>
       </c>
       <c r="D2" t="n">
-        <v>24972</v>
+        <v>25851</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2296</v>
+        <v>2805</v>
       </c>
       <c r="C3" t="n">
-        <v>4725</v>
+        <v>4048</v>
       </c>
       <c r="D3" t="n">
-        <v>1482</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4425</v>
+        <v>6034</v>
       </c>
       <c r="C2" t="n">
-        <v>8524</v>
+        <v>5300</v>
       </c>
       <c r="D2" t="n">
-        <v>27674</v>
+        <v>22223</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3373</v>
+        <v>4522</v>
       </c>
       <c r="C3" t="n">
-        <v>4882</v>
+        <v>4476</v>
       </c>
       <c r="D3" t="n">
-        <v>5319</v>
+        <v>7252</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1031</v>
+        <v>1253</v>
       </c>
       <c r="C4" t="n">
-        <v>2811</v>
+        <v>2416</v>
       </c>
       <c r="D4" t="n">
-        <v>1479</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4426</v>
+        <v>5419</v>
       </c>
       <c r="C2" t="n">
-        <v>5670</v>
+        <v>5869</v>
       </c>
       <c r="D2" t="n">
-        <v>23467</v>
+        <v>27495</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3200</v>
+        <v>4330</v>
       </c>
       <c r="C3" t="n">
-        <v>5923</v>
+        <v>4263</v>
       </c>
       <c r="D3" t="n">
-        <v>8512</v>
+        <v>9125</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1873</v>
+        <v>2453</v>
       </c>
       <c r="C4" t="n">
-        <v>3878</v>
+        <v>3489</v>
       </c>
       <c r="D4" t="n">
-        <v>2171</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>474</v>
+        <v>565</v>
       </c>
       <c r="C5" t="n">
-        <v>1634</v>
+        <v>1419</v>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5319,7 +5319,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4696</v>
+        <v>7176</v>
       </c>
       <c r="C2" t="n">
-        <v>7991</v>
+        <v>7925</v>
       </c>
       <c r="D2" t="n">
-        <v>22770</v>
+        <v>29948</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3101</v>
+        <v>3986</v>
       </c>
       <c r="C3" t="n">
-        <v>5042</v>
+        <v>4423</v>
       </c>
       <c r="D3" t="n">
-        <v>10185</v>
+        <v>11274</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2131</v>
+        <v>2846</v>
       </c>
       <c r="C4" t="n">
-        <v>4896</v>
+        <v>3791</v>
       </c>
       <c r="D4" t="n">
-        <v>3261</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>967</v>
+        <v>1238</v>
       </c>
       <c r="C5" t="n">
-        <v>2763</v>
+        <v>2462</v>
       </c>
       <c r="D5" t="n">
-        <v>1320</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>962</v>
+        <v>859</v>
       </c>
       <c r="D6" t="n">
-        <v>942</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>101</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4887</v>
+        <v>7285</v>
       </c>
       <c r="C2" t="n">
-        <v>8658</v>
+        <v>10991</v>
       </c>
       <c r="D2" t="n">
-        <v>29740</v>
+        <v>29951</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2818</v>
+        <v>3986</v>
       </c>
       <c r="C3" t="n">
-        <v>5344</v>
+        <v>5064</v>
       </c>
       <c r="D3" t="n">
-        <v>10707</v>
+        <v>12530</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1625</v>
+        <v>2096</v>
       </c>
       <c r="C4" t="n">
-        <v>4033</v>
+        <v>3381</v>
       </c>
       <c r="D4" t="n">
-        <v>3861</v>
+        <v>4510</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>801</v>
+        <v>1053</v>
       </c>
       <c r="C5" t="n">
-        <v>2826</v>
+        <v>2271</v>
       </c>
       <c r="D5" t="n">
-        <v>1298</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="C6" t="n">
-        <v>1241</v>
+        <v>1112</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>416</v>
+        <v>378</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4393</v>
+        <v>5809</v>
       </c>
       <c r="C2" t="n">
-        <v>5072</v>
+        <v>5953</v>
       </c>
       <c r="D2" t="n">
-        <v>21754</v>
+        <v>28153</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3185</v>
+        <v>4660</v>
       </c>
       <c r="C3" t="n">
-        <v>6261</v>
+        <v>7298</v>
       </c>
       <c r="D3" t="n">
-        <v>13116</v>
+        <v>14534</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1926</v>
+        <v>2658</v>
       </c>
       <c r="C4" t="n">
-        <v>4742</v>
+        <v>4312</v>
       </c>
       <c r="D4" t="n">
-        <v>5086</v>
+        <v>5989</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1083</v>
+        <v>1389</v>
       </c>
       <c r="C5" t="n">
-        <v>3474</v>
+        <v>2841</v>
       </c>
       <c r="D5" t="n">
-        <v>1775</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>504</v>
+        <v>653</v>
       </c>
       <c r="C6" t="n">
-        <v>2123</v>
+        <v>1754</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>929</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="C7" t="n">
-        <v>876</v>
+        <v>787</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4053</v>
+        <v>5992</v>
       </c>
       <c r="C2" t="n">
-        <v>9135</v>
+        <v>8907</v>
       </c>
       <c r="D2" t="n">
-        <v>21467</v>
+        <v>21875</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3106</v>
+        <v>4295</v>
       </c>
       <c r="C3" t="n">
-        <v>4877</v>
+        <v>5704</v>
       </c>
       <c r="D3" t="n">
-        <v>13553</v>
+        <v>15666</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2199</v>
+        <v>3106</v>
       </c>
       <c r="C4" t="n">
-        <v>5443</v>
+        <v>5884</v>
       </c>
       <c r="D4" t="n">
-        <v>6473</v>
+        <v>7447</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1311</v>
+        <v>1770</v>
       </c>
       <c r="C5" t="n">
-        <v>4095</v>
+        <v>3572</v>
       </c>
       <c r="D5" t="n">
-        <v>2307</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>915</v>
       </c>
       <c r="C6" t="n">
-        <v>2812</v>
+        <v>2280</v>
       </c>
       <c r="D6" t="n">
-        <v>1012</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>375</v>
       </c>
       <c r="C7" t="n">
-        <v>1523</v>
+        <v>1288</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>597</v>
+        <v>546</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D9" t="n">
         <v>297</v>
@@ -6493,7 +6493,7 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
         <v>238</v>
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_44_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7125</v>
+        <v>5392</v>
       </c>
       <c r="C2" t="n">
-        <v>7058</v>
+        <v>10665</v>
       </c>
       <c r="D2" t="n">
-        <v>19635</v>
+        <v>25549</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4158</v>
+        <v>3679</v>
       </c>
       <c r="C3" t="n">
-        <v>6350</v>
+        <v>5194</v>
       </c>
       <c r="D3" t="n">
-        <v>15482</v>
+        <v>16748</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3118</v>
+        <v>3005</v>
       </c>
       <c r="C4" t="n">
-        <v>5613</v>
+        <v>5382</v>
       </c>
       <c r="D4" t="n">
-        <v>8640</v>
+        <v>8113</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2102</v>
+        <v>1846</v>
       </c>
       <c r="C5" t="n">
-        <v>4651</v>
+        <v>4005</v>
       </c>
       <c r="D5" t="n">
-        <v>3360</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1177</v>
+        <v>1005</v>
       </c>
       <c r="C6" t="n">
-        <v>2876</v>
+        <v>2394</v>
       </c>
       <c r="D6" t="n">
-        <v>1342</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>549</v>
+        <v>471</v>
       </c>
       <c r="C7" t="n">
-        <v>1741</v>
+        <v>1368</v>
       </c>
       <c r="D7" t="n">
-        <v>681</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="C8" t="n">
-        <v>887</v>
+        <v>671</v>
       </c>
       <c r="D8" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>380</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7476</v>
+        <v>6811</v>
       </c>
       <c r="C2" t="n">
-        <v>5454</v>
+        <v>11994</v>
       </c>
       <c r="D2" t="n">
-        <v>16424</v>
+        <v>25812</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4462</v>
+        <v>3629</v>
       </c>
       <c r="C3" t="n">
-        <v>5875</v>
+        <v>6794</v>
       </c>
       <c r="D3" t="n">
-        <v>15006</v>
+        <v>16819</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3037</v>
+        <v>2827</v>
       </c>
       <c r="C4" t="n">
-        <v>5842</v>
+        <v>5178</v>
       </c>
       <c r="D4" t="n">
-        <v>9493</v>
+        <v>9197</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2240</v>
+        <v>2073</v>
       </c>
       <c r="C5" t="n">
-        <v>4943</v>
+        <v>4530</v>
       </c>
       <c r="D5" t="n">
-        <v>4036</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>1258</v>
       </c>
       <c r="C6" t="n">
-        <v>3632</v>
+        <v>3112</v>
       </c>
       <c r="D6" t="n">
-        <v>1633</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>732</v>
+        <v>627</v>
       </c>
       <c r="C7" t="n">
-        <v>2212</v>
+        <v>1816</v>
       </c>
       <c r="D7" t="n">
-        <v>764</v>
+        <v>721</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="C8" t="n">
-        <v>1246</v>
+        <v>978</v>
       </c>
       <c r="D8" t="n">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C9" t="n">
-        <v>579</v>
+        <v>466</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8653</v>
+        <v>7843</v>
       </c>
       <c r="C2" t="n">
-        <v>5336</v>
+        <v>15733</v>
       </c>
       <c r="D2" t="n">
-        <v>21174</v>
+        <v>28269</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4607</v>
+        <v>4011</v>
       </c>
       <c r="C3" t="n">
-        <v>5121</v>
+        <v>8031</v>
       </c>
       <c r="D3" t="n">
-        <v>14215</v>
+        <v>16866</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3062</v>
+        <v>2723</v>
       </c>
       <c r="C4" t="n">
-        <v>5678</v>
+        <v>5734</v>
       </c>
       <c r="D4" t="n">
-        <v>9907</v>
+        <v>10088</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2276</v>
+        <v>2117</v>
       </c>
       <c r="C5" t="n">
-        <v>5163</v>
+        <v>4672</v>
       </c>
       <c r="D5" t="n">
-        <v>4699</v>
+        <v>4283</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1592</v>
+        <v>1445</v>
       </c>
       <c r="C6" t="n">
-        <v>4128</v>
+        <v>3682</v>
       </c>
       <c r="D6" t="n">
-        <v>1918</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>906</v>
+        <v>789</v>
       </c>
       <c r="C7" t="n">
-        <v>2746</v>
+        <v>2330</v>
       </c>
       <c r="D7" t="n">
-        <v>875</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="C8" t="n">
-        <v>1602</v>
+        <v>1304</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="C9" t="n">
-        <v>827</v>
+        <v>666</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>381</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7952</v>
+        <v>7138</v>
       </c>
       <c r="C2" t="n">
-        <v>3671</v>
+        <v>10572</v>
       </c>
       <c r="D2" t="n">
-        <v>17621</v>
+        <v>23262</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5513</v>
+        <v>4883</v>
       </c>
       <c r="C3" t="n">
-        <v>7857</v>
+        <v>12035</v>
       </c>
       <c r="D3" t="n">
-        <v>16007</v>
+        <v>18545</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2103</v>
+        <v>1956</v>
       </c>
       <c r="C4" t="n">
-        <v>8063</v>
+        <v>7677</v>
       </c>
       <c r="D4" t="n">
-        <v>9715</v>
+        <v>9601</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1471</v>
+        <v>1335</v>
       </c>
       <c r="C5" t="n">
-        <v>4045</v>
+        <v>3608</v>
       </c>
       <c r="D5" t="n">
-        <v>3142</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>837</v>
+        <v>729</v>
       </c>
       <c r="C6" t="n">
-        <v>2691</v>
+        <v>2283</v>
       </c>
       <c r="D6" t="n">
-        <v>857</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="C7" t="n">
-        <v>1569</v>
+        <v>1277</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>810</v>
+        <v>652</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4930</v>
+        <v>4438</v>
       </c>
       <c r="C2" t="n">
-        <v>1902</v>
+        <v>5289</v>
       </c>
       <c r="D2" t="n">
-        <v>12155</v>
+        <v>17526</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5644</v>
+        <v>5045</v>
       </c>
       <c r="C3" t="n">
-        <v>5419</v>
+        <v>10290</v>
       </c>
       <c r="D3" t="n">
-        <v>15458</v>
+        <v>18118</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2940</v>
+        <v>2705</v>
       </c>
       <c r="C4" t="n">
-        <v>8032</v>
+        <v>9862</v>
       </c>
       <c r="D4" t="n">
-        <v>10418</v>
+        <v>10867</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1630</v>
+        <v>1477</v>
       </c>
       <c r="C5" t="n">
-        <v>5813</v>
+        <v>5351</v>
       </c>
       <c r="D5" t="n">
-        <v>3927</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>879</v>
       </c>
       <c r="C6" t="n">
-        <v>3323</v>
+        <v>2892</v>
       </c>
       <c r="D6" t="n">
-        <v>1091</v>
+        <v>992</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="C7" t="n">
-        <v>1988</v>
+        <v>1665</v>
       </c>
       <c r="D7" t="n">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1060</v>
+        <v>848</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +2125,10 @@
         <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>375</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5891</v>
+        <v>5763</v>
       </c>
       <c r="C2" t="n">
-        <v>2872</v>
+        <v>13197</v>
       </c>
       <c r="D2" t="n">
-        <v>11272</v>
+        <v>17928</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4533</v>
+        <v>4019</v>
       </c>
       <c r="C3" t="n">
-        <v>3340</v>
+        <v>7040</v>
       </c>
       <c r="D3" t="n">
-        <v>13970</v>
+        <v>16960</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3499</v>
+        <v>3211</v>
       </c>
       <c r="C4" t="n">
-        <v>6585</v>
+        <v>9866</v>
       </c>
       <c r="D4" t="n">
-        <v>10923</v>
+        <v>11720</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1940</v>
+        <v>1772</v>
       </c>
       <c r="C5" t="n">
-        <v>6735</v>
+        <v>7361</v>
       </c>
       <c r="D5" t="n">
-        <v>4804</v>
+        <v>4654</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1162</v>
+        <v>1035</v>
       </c>
       <c r="C6" t="n">
-        <v>4446</v>
+        <v>4001</v>
       </c>
       <c r="D6" t="n">
-        <v>1484</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>524</v>
+        <v>472</v>
       </c>
       <c r="C7" t="n">
-        <v>2582</v>
+        <v>2193</v>
       </c>
       <c r="D7" t="n">
-        <v>602</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>1442</v>
+        <v>1192</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -2436,10 +2436,10 @@
         <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>659</v>
+        <v>562</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3499</v>
+        <v>3396</v>
       </c>
       <c r="C2" t="n">
-        <v>1359</v>
+        <v>6143</v>
       </c>
       <c r="D2" t="n">
-        <v>7885</v>
+        <v>12504</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4688</v>
+        <v>4281</v>
       </c>
       <c r="C3" t="n">
-        <v>3081</v>
+        <v>8894</v>
       </c>
       <c r="D3" t="n">
-        <v>13376</v>
+        <v>16680</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3880</v>
+        <v>3542</v>
       </c>
       <c r="C4" t="n">
-        <v>6021</v>
+        <v>9685</v>
       </c>
       <c r="D4" t="n">
-        <v>11424</v>
+        <v>12423</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2035</v>
+        <v>1845</v>
       </c>
       <c r="C5" t="n">
-        <v>7686</v>
+        <v>9032</v>
       </c>
       <c r="D5" t="n">
-        <v>5040</v>
+        <v>4907</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>956</v>
+        <v>856</v>
       </c>
       <c r="C6" t="n">
-        <v>5336</v>
+        <v>4726</v>
       </c>
       <c r="D6" t="n">
-        <v>1441</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>2695</v>
+        <v>2267</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1083</v>
+        <v>912</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4729</v>
+        <v>3593</v>
       </c>
       <c r="C2" t="n">
-        <v>6719</v>
+        <v>6179</v>
       </c>
       <c r="D2" t="n">
-        <v>10359</v>
+        <v>16183</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3572</v>
+        <v>3338</v>
       </c>
       <c r="C3" t="n">
-        <v>2033</v>
+        <v>6811</v>
       </c>
       <c r="D3" t="n">
-        <v>11730</v>
+        <v>15151</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3713</v>
+        <v>3384</v>
       </c>
       <c r="C4" t="n">
-        <v>4542</v>
+        <v>9204</v>
       </c>
       <c r="D4" t="n">
-        <v>11395</v>
+        <v>12699</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2468</v>
+        <v>2232</v>
       </c>
       <c r="C5" t="n">
-        <v>6848</v>
+        <v>9219</v>
       </c>
       <c r="D5" t="n">
-        <v>5915</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1246</v>
+        <v>1105</v>
       </c>
       <c r="C6" t="n">
-        <v>6331</v>
+        <v>6507</v>
       </c>
       <c r="D6" t="n">
-        <v>1905</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>3807</v>
+        <v>3274</v>
       </c>
       <c r="D7" t="n">
-        <v>704</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>1688</v>
+        <v>1407</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>553</v>
+        <v>482</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3375</v>
+        <v>2460</v>
       </c>
       <c r="C2" t="n">
-        <v>4069</v>
+        <v>3338</v>
       </c>
       <c r="D2" t="n">
-        <v>8667</v>
+        <v>11988</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3461</v>
+        <v>2996</v>
       </c>
       <c r="C3" t="n">
-        <v>3585</v>
+        <v>6032</v>
       </c>
       <c r="D3" t="n">
-        <v>10927</v>
+        <v>14596</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3379</v>
+        <v>3073</v>
       </c>
       <c r="C4" t="n">
-        <v>3542</v>
+        <v>8247</v>
       </c>
       <c r="D4" t="n">
-        <v>11203</v>
+        <v>12740</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2711</v>
+        <v>2449</v>
       </c>
       <c r="C5" t="n">
-        <v>6061</v>
+        <v>9375</v>
       </c>
       <c r="D5" t="n">
-        <v>6480</v>
+        <v>6442</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1459</v>
+        <v>1295</v>
       </c>
       <c r="C6" t="n">
-        <v>6760</v>
+        <v>7589</v>
       </c>
       <c r="D6" t="n">
-        <v>2265</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>334</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>4709</v>
+        <v>4257</v>
       </c>
       <c r="D7" t="n">
-        <v>802</v>
+        <v>756</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>2227</v>
+        <v>1828</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>647</v>
+        <v>551</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4404</v>
+        <v>4918</v>
       </c>
       <c r="C2" t="n">
-        <v>8227</v>
+        <v>9688</v>
       </c>
       <c r="D2" t="n">
-        <v>10626</v>
+        <v>24009</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2883</v>
+        <v>2367</v>
       </c>
       <c r="C3" t="n">
-        <v>3390</v>
+        <v>4448</v>
       </c>
       <c r="D3" t="n">
-        <v>9956</v>
+        <v>13489</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2991</v>
+        <v>2673</v>
       </c>
       <c r="C4" t="n">
-        <v>3486</v>
+        <v>7161</v>
       </c>
       <c r="D4" t="n">
-        <v>10822</v>
+        <v>12479</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2682</v>
+        <v>2421</v>
       </c>
       <c r="C5" t="n">
-        <v>4895</v>
+        <v>8736</v>
       </c>
       <c r="D5" t="n">
-        <v>6855</v>
+        <v>7092</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1758</v>
+        <v>1552</v>
       </c>
       <c r="C6" t="n">
-        <v>6426</v>
+        <v>8195</v>
       </c>
       <c r="D6" t="n">
-        <v>2802</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>619</v>
+        <v>523</v>
       </c>
       <c r="C7" t="n">
-        <v>5491</v>
+        <v>5463</v>
       </c>
       <c r="D7" t="n">
-        <v>980</v>
+        <v>914</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>3147</v>
+        <v>2678</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1179</v>
+        <v>956</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6603</v>
+        <v>5049</v>
       </c>
       <c r="C2" t="n">
-        <v>8032</v>
+        <v>4612</v>
       </c>
       <c r="D2" t="n">
-        <v>19036</v>
+        <v>7459</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3118</v>
+        <v>3592</v>
       </c>
       <c r="C2" t="n">
-        <v>4607</v>
+        <v>5658</v>
       </c>
       <c r="D2" t="n">
-        <v>7820</v>
+        <v>17862</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3821</v>
+        <v>3258</v>
       </c>
       <c r="C3" t="n">
-        <v>4838</v>
+        <v>5978</v>
       </c>
       <c r="D3" t="n">
-        <v>10965</v>
+        <v>15252</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3984</v>
+        <v>3603</v>
       </c>
       <c r="C4" t="n">
-        <v>5193</v>
+        <v>10110</v>
       </c>
       <c r="D4" t="n">
-        <v>11241</v>
+        <v>12723</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1723</v>
+        <v>1456</v>
       </c>
       <c r="C5" t="n">
-        <v>8217</v>
+        <v>12120</v>
       </c>
       <c r="D5" t="n">
-        <v>6374</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>571</v>
+        <v>483</v>
       </c>
       <c r="C6" t="n">
-        <v>6703</v>
+        <v>6799</v>
       </c>
       <c r="D6" t="n">
-        <v>2208</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>3084</v>
+        <v>2624</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1155</v>
+        <v>936</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
         <v>61</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8214</v>
+        <v>6600</v>
       </c>
       <c r="C2" t="n">
-        <v>6068</v>
+        <v>4846</v>
       </c>
       <c r="D2" t="n">
-        <v>25851</v>
+        <v>13209</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2805</v>
+        <v>2146</v>
       </c>
       <c r="C3" t="n">
-        <v>4048</v>
+        <v>2361</v>
       </c>
       <c r="D3" t="n">
-        <v>3837</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6034</v>
+        <v>4204</v>
       </c>
       <c r="C2" t="n">
-        <v>5300</v>
+        <v>4062</v>
       </c>
       <c r="D2" t="n">
-        <v>22223</v>
+        <v>18948</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4522</v>
+        <v>3588</v>
       </c>
       <c r="C3" t="n">
-        <v>4476</v>
+        <v>3264</v>
       </c>
       <c r="D3" t="n">
-        <v>7252</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1253</v>
+        <v>966</v>
       </c>
       <c r="C4" t="n">
-        <v>2416</v>
+        <v>1449</v>
       </c>
       <c r="D4" t="n">
-        <v>1954</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5419</v>
+        <v>5540</v>
       </c>
       <c r="C2" t="n">
-        <v>5869</v>
+        <v>6048</v>
       </c>
       <c r="D2" t="n">
-        <v>27495</v>
+        <v>30636</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4330</v>
+        <v>3240</v>
       </c>
       <c r="C3" t="n">
-        <v>4263</v>
+        <v>3201</v>
       </c>
       <c r="D3" t="n">
-        <v>9125</v>
+        <v>5872</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2453</v>
+        <v>1925</v>
       </c>
       <c r="C4" t="n">
-        <v>3489</v>
+        <v>2432</v>
       </c>
       <c r="D4" t="n">
-        <v>2911</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>565</v>
+        <v>457</v>
       </c>
       <c r="C5" t="n">
-        <v>1419</v>
+        <v>899</v>
       </c>
       <c r="D5" t="n">
-        <v>1287</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7176</v>
+        <v>5538</v>
       </c>
       <c r="C2" t="n">
-        <v>7925</v>
+        <v>5947</v>
       </c>
       <c r="D2" t="n">
-        <v>29948</v>
+        <v>34206</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3986</v>
+        <v>3546</v>
       </c>
       <c r="C3" t="n">
-        <v>4423</v>
+        <v>4079</v>
       </c>
       <c r="D3" t="n">
-        <v>11274</v>
+        <v>9222</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2846</v>
+        <v>2183</v>
       </c>
       <c r="C4" t="n">
-        <v>3791</v>
+        <v>2802</v>
       </c>
       <c r="D4" t="n">
-        <v>3955</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1238</v>
+        <v>990</v>
       </c>
       <c r="C5" t="n">
-        <v>2462</v>
+        <v>1689</v>
       </c>
       <c r="D5" t="n">
-        <v>1516</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>303</v>
+        <v>262</v>
       </c>
       <c r="C6" t="n">
-        <v>859</v>
+        <v>599</v>
       </c>
       <c r="D6" t="n">
-        <v>960</v>
+        <v>949</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7285</v>
+        <v>6823</v>
       </c>
       <c r="C2" t="n">
-        <v>10991</v>
+        <v>9483</v>
       </c>
       <c r="D2" t="n">
-        <v>29951</v>
+        <v>36147</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3986</v>
+        <v>3299</v>
       </c>
       <c r="C3" t="n">
-        <v>5064</v>
+        <v>4135</v>
       </c>
       <c r="D3" t="n">
-        <v>12530</v>
+        <v>11637</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2096</v>
+        <v>1789</v>
       </c>
       <c r="C4" t="n">
-        <v>3381</v>
+        <v>2885</v>
       </c>
       <c r="D4" t="n">
-        <v>4510</v>
+        <v>3216</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1053</v>
+        <v>827</v>
       </c>
       <c r="C5" t="n">
-        <v>2271</v>
+        <v>1652</v>
       </c>
       <c r="D5" t="n">
-        <v>1520</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="C6" t="n">
-        <v>1112</v>
+        <v>781</v>
       </c>
       <c r="D6" t="n">
-        <v>803</v>
+        <v>761</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>378</v>
+        <v>305</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,10 +5997,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5809</v>
+        <v>6379</v>
       </c>
       <c r="C2" t="n">
-        <v>5953</v>
+        <v>7385</v>
       </c>
       <c r="D2" t="n">
-        <v>28153</v>
+        <v>26183</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4660</v>
+        <v>4214</v>
       </c>
       <c r="C3" t="n">
-        <v>7298</v>
+        <v>6284</v>
       </c>
       <c r="D3" t="n">
-        <v>14534</v>
+        <v>15075</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2658</v>
+        <v>2221</v>
       </c>
       <c r="C4" t="n">
-        <v>4312</v>
+        <v>3592</v>
       </c>
       <c r="D4" t="n">
-        <v>5989</v>
+        <v>4896</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1389</v>
+        <v>1174</v>
       </c>
       <c r="C5" t="n">
-        <v>2841</v>
+        <v>2351</v>
       </c>
       <c r="D5" t="n">
-        <v>2033</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>653</v>
+        <v>524</v>
       </c>
       <c r="C6" t="n">
-        <v>1754</v>
+        <v>1273</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>829</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>787</v>
+        <v>575</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5992</v>
+        <v>4564</v>
       </c>
       <c r="C2" t="n">
-        <v>8907</v>
+        <v>5956</v>
       </c>
       <c r="D2" t="n">
-        <v>21875</v>
+        <v>29531</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4295</v>
+        <v>4346</v>
       </c>
       <c r="C3" t="n">
-        <v>5704</v>
+        <v>5957</v>
       </c>
       <c r="D3" t="n">
-        <v>15666</v>
+        <v>15766</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3106</v>
+        <v>2779</v>
       </c>
       <c r="C4" t="n">
-        <v>5884</v>
+        <v>5067</v>
       </c>
       <c r="D4" t="n">
-        <v>7447</v>
+        <v>6654</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1770</v>
+        <v>1483</v>
       </c>
       <c r="C5" t="n">
-        <v>3572</v>
+        <v>2993</v>
       </c>
       <c r="D5" t="n">
-        <v>2692</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>915</v>
+        <v>776</v>
       </c>
       <c r="C6" t="n">
-        <v>2280</v>
+        <v>1837</v>
       </c>
       <c r="D6" t="n">
-        <v>1097</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>375</v>
+        <v>308</v>
       </c>
       <c r="C7" t="n">
-        <v>1288</v>
+        <v>938</v>
       </c>
       <c r="D7" t="n">
-        <v>619</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>546</v>
+        <v>425</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_44_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_44_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5392</v>
+        <v>1020</v>
       </c>
       <c r="C2" t="n">
-        <v>10665</v>
+        <v>4036</v>
       </c>
       <c r="D2" t="n">
-        <v>25549</v>
+        <v>14098</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3679</v>
+        <v>2129</v>
       </c>
       <c r="C3" t="n">
-        <v>5194</v>
+        <v>7858</v>
       </c>
       <c r="D3" t="n">
-        <v>16748</v>
+        <v>12676</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3005</v>
+        <v>1479</v>
       </c>
       <c r="C4" t="n">
-        <v>5382</v>
+        <v>7959</v>
       </c>
       <c r="D4" t="n">
-        <v>8113</v>
+        <v>5183</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1846</v>
+        <v>701</v>
       </c>
       <c r="C5" t="n">
-        <v>4005</v>
+        <v>3929</v>
       </c>
       <c r="D5" t="n">
-        <v>2855</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1005</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>2394</v>
+        <v>1319</v>
       </c>
       <c r="D6" t="n">
-        <v>1150</v>
+        <v>738</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>471</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>1368</v>
+        <v>581</v>
       </c>
       <c r="D7" t="n">
-        <v>650</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>671</v>
+        <v>343</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
+        <v>292</v>
+      </c>
+      <c r="D9" t="n">
         <v>323</v>
-      </c>
-      <c r="D9" t="n">
-        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>53</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6811</v>
+        <v>1637</v>
       </c>
       <c r="C2" t="n">
-        <v>11994</v>
+        <v>4974</v>
       </c>
       <c r="D2" t="n">
-        <v>25812</v>
+        <v>19621</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3629</v>
+        <v>1361</v>
       </c>
       <c r="C3" t="n">
-        <v>6794</v>
+        <v>5073</v>
       </c>
       <c r="D3" t="n">
-        <v>16819</v>
+        <v>11990</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2827</v>
+        <v>1558</v>
       </c>
       <c r="C4" t="n">
-        <v>5178</v>
+        <v>7737</v>
       </c>
       <c r="D4" t="n">
-        <v>9197</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2073</v>
+        <v>936</v>
       </c>
       <c r="C5" t="n">
-        <v>4530</v>
+        <v>6051</v>
       </c>
       <c r="D5" t="n">
-        <v>3626</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1258</v>
+        <v>435</v>
       </c>
       <c r="C6" t="n">
-        <v>3112</v>
+        <v>2645</v>
       </c>
       <c r="D6" t="n">
-        <v>1385</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>627</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>1816</v>
+        <v>948</v>
       </c>
       <c r="D7" t="n">
-        <v>721</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>263</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>978</v>
+        <v>455</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>466</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7843</v>
+        <v>860</v>
       </c>
       <c r="C2" t="n">
-        <v>15733</v>
+        <v>2012</v>
       </c>
       <c r="D2" t="n">
-        <v>28269</v>
+        <v>13195</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4011</v>
+        <v>1386</v>
       </c>
       <c r="C3" t="n">
-        <v>8031</v>
+        <v>4814</v>
       </c>
       <c r="D3" t="n">
-        <v>16866</v>
+        <v>12640</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2723</v>
+        <v>1680</v>
       </c>
       <c r="C4" t="n">
-        <v>5734</v>
+        <v>7318</v>
       </c>
       <c r="D4" t="n">
-        <v>10088</v>
+        <v>7214</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2117</v>
+        <v>944</v>
       </c>
       <c r="C5" t="n">
-        <v>4672</v>
+        <v>7207</v>
       </c>
       <c r="D5" t="n">
-        <v>4283</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1445</v>
+        <v>354</v>
       </c>
       <c r="C6" t="n">
-        <v>3682</v>
+        <v>3588</v>
       </c>
       <c r="D6" t="n">
-        <v>1689</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>789</v>
+        <v>76</v>
       </c>
       <c r="C7" t="n">
-        <v>2330</v>
+        <v>968</v>
       </c>
       <c r="D7" t="n">
-        <v>797</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>359</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1304</v>
+        <v>477</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>666</v>
+        <v>243</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7138</v>
+        <v>1056</v>
       </c>
       <c r="C2" t="n">
-        <v>10572</v>
+        <v>8923</v>
       </c>
       <c r="D2" t="n">
-        <v>23262</v>
+        <v>15877</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4883</v>
+        <v>972</v>
       </c>
       <c r="C3" t="n">
-        <v>12035</v>
+        <v>2950</v>
       </c>
       <c r="D3" t="n">
-        <v>18545</v>
+        <v>11834</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1956</v>
+        <v>1375</v>
       </c>
       <c r="C4" t="n">
-        <v>7677</v>
+        <v>5889</v>
       </c>
       <c r="D4" t="n">
-        <v>9601</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1335</v>
+        <v>1136</v>
       </c>
       <c r="C5" t="n">
-        <v>3608</v>
+        <v>7182</v>
       </c>
       <c r="D5" t="n">
-        <v>2847</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>729</v>
+        <v>545</v>
       </c>
       <c r="C6" t="n">
-        <v>2283</v>
+        <v>5358</v>
       </c>
       <c r="D6" t="n">
-        <v>781</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>1277</v>
+        <v>2167</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>652</v>
+        <v>688</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4438</v>
+        <v>553</v>
       </c>
       <c r="C2" t="n">
-        <v>5289</v>
+        <v>4014</v>
       </c>
       <c r="D2" t="n">
-        <v>17526</v>
+        <v>11870</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5045</v>
+        <v>876</v>
       </c>
       <c r="C3" t="n">
-        <v>10290</v>
+        <v>5156</v>
       </c>
       <c r="D3" t="n">
-        <v>18118</v>
+        <v>11702</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2705</v>
+        <v>1141</v>
       </c>
       <c r="C4" t="n">
-        <v>9862</v>
+        <v>4553</v>
       </c>
       <c r="D4" t="n">
-        <v>10867</v>
+        <v>8409</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1477</v>
+        <v>1188</v>
       </c>
       <c r="C5" t="n">
-        <v>5351</v>
+        <v>6762</v>
       </c>
       <c r="D5" t="n">
-        <v>3658</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>879</v>
+        <v>666</v>
       </c>
       <c r="C6" t="n">
-        <v>2892</v>
+        <v>6243</v>
       </c>
       <c r="D6" t="n">
-        <v>992</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>1665</v>
+        <v>3284</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>679</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>848</v>
+        <v>1074</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
+        <v>433</v>
+      </c>
+      <c r="D9" t="n">
         <v>375</v>
-      </c>
-      <c r="D9" t="n">
-        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5763</v>
+        <v>749</v>
       </c>
       <c r="C2" t="n">
-        <v>13197</v>
+        <v>4704</v>
       </c>
       <c r="D2" t="n">
-        <v>17928</v>
+        <v>11559</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4019</v>
+        <v>623</v>
       </c>
       <c r="C3" t="n">
-        <v>7040</v>
+        <v>4095</v>
       </c>
       <c r="D3" t="n">
-        <v>16960</v>
+        <v>10938</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3211</v>
+        <v>906</v>
       </c>
       <c r="C4" t="n">
-        <v>9866</v>
+        <v>4753</v>
       </c>
       <c r="D4" t="n">
-        <v>11720</v>
+        <v>8690</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1772</v>
+        <v>1081</v>
       </c>
       <c r="C5" t="n">
-        <v>7361</v>
+        <v>5647</v>
       </c>
       <c r="D5" t="n">
-        <v>4654</v>
+        <v>4527</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1035</v>
+        <v>807</v>
       </c>
       <c r="C6" t="n">
-        <v>4001</v>
+        <v>6412</v>
       </c>
       <c r="D6" t="n">
-        <v>1362</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>472</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>2193</v>
+        <v>4590</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="C8" t="n">
-        <v>1192</v>
+        <v>1972</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>562</v>
+        <v>675</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
+        <v>186</v>
+      </c>
+      <c r="D11" t="n">
         <v>187</v>
-      </c>
-      <c r="D11" t="n">
-        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3396</v>
+        <v>497</v>
       </c>
       <c r="C2" t="n">
-        <v>6143</v>
+        <v>2446</v>
       </c>
       <c r="D2" t="n">
-        <v>12504</v>
+        <v>8323</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4281</v>
+        <v>879</v>
       </c>
       <c r="C3" t="n">
-        <v>8894</v>
+        <v>4580</v>
       </c>
       <c r="D3" t="n">
-        <v>16680</v>
+        <v>11737</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3542</v>
+        <v>1443</v>
       </c>
       <c r="C4" t="n">
-        <v>9685</v>
+        <v>6640</v>
       </c>
       <c r="D4" t="n">
-        <v>12423</v>
+        <v>9029</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1845</v>
+        <v>825</v>
       </c>
       <c r="C5" t="n">
-        <v>9032</v>
+        <v>8661</v>
       </c>
       <c r="D5" t="n">
-        <v>4907</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>856</v>
+        <v>295</v>
       </c>
       <c r="C6" t="n">
-        <v>4726</v>
+        <v>6131</v>
       </c>
       <c r="D6" t="n">
-        <v>1330</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>2267</v>
+        <v>1932</v>
       </c>
       <c r="D7" t="n">
-        <v>582</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>912</v>
+        <v>661</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
+        <v>182</v>
+      </c>
+      <c r="D10" t="n">
         <v>183</v>
-      </c>
-      <c r="D10" t="n">
-        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3593</v>
+        <v>287</v>
       </c>
       <c r="C2" t="n">
-        <v>6179</v>
+        <v>1503</v>
       </c>
       <c r="D2" t="n">
-        <v>16183</v>
+        <v>6491</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3338</v>
+        <v>610</v>
       </c>
       <c r="C3" t="n">
-        <v>6811</v>
+        <v>3088</v>
       </c>
       <c r="D3" t="n">
-        <v>15151</v>
+        <v>10404</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3384</v>
+        <v>985</v>
       </c>
       <c r="C4" t="n">
-        <v>9204</v>
+        <v>5285</v>
       </c>
       <c r="D4" t="n">
-        <v>12699</v>
+        <v>8839</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2232</v>
+        <v>775</v>
       </c>
       <c r="C5" t="n">
-        <v>9219</v>
+        <v>6830</v>
       </c>
       <c r="D5" t="n">
-        <v>5840</v>
+        <v>4357</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1105</v>
+        <v>294</v>
       </c>
       <c r="C6" t="n">
-        <v>6507</v>
+        <v>5943</v>
       </c>
       <c r="D6" t="n">
-        <v>1793</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>69</v>
       </c>
       <c r="C7" t="n">
-        <v>3274</v>
+        <v>2712</v>
       </c>
       <c r="D7" t="n">
-        <v>677</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1407</v>
+        <v>752</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>482</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2460</v>
+        <v>502</v>
       </c>
       <c r="C2" t="n">
-        <v>3338</v>
+        <v>6160</v>
       </c>
       <c r="D2" t="n">
-        <v>11988</v>
+        <v>7288</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2996</v>
+        <v>382</v>
       </c>
       <c r="C3" t="n">
-        <v>6032</v>
+        <v>1924</v>
       </c>
       <c r="D3" t="n">
-        <v>14596</v>
+        <v>9028</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3073</v>
+        <v>702</v>
       </c>
       <c r="C4" t="n">
-        <v>8247</v>
+        <v>3930</v>
       </c>
       <c r="D4" t="n">
-        <v>12740</v>
+        <v>8870</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2449</v>
+        <v>794</v>
       </c>
       <c r="C5" t="n">
-        <v>9375</v>
+        <v>5908</v>
       </c>
       <c r="D5" t="n">
-        <v>6442</v>
+        <v>5042</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1295</v>
+        <v>470</v>
       </c>
       <c r="C6" t="n">
-        <v>7589</v>
+        <v>6394</v>
       </c>
       <c r="D6" t="n">
-        <v>2173</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>4257</v>
+        <v>4325</v>
       </c>
       <c r="D7" t="n">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>1828</v>
+        <v>1700</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>551</v>
+        <v>490</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4918</v>
+        <v>581</v>
       </c>
       <c r="C2" t="n">
-        <v>9688</v>
+        <v>5571</v>
       </c>
       <c r="D2" t="n">
-        <v>24009</v>
+        <v>11072</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2367</v>
+        <v>359</v>
       </c>
       <c r="C3" t="n">
-        <v>4448</v>
+        <v>3510</v>
       </c>
       <c r="D3" t="n">
-        <v>13489</v>
+        <v>8156</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2673</v>
+        <v>487</v>
       </c>
       <c r="C4" t="n">
-        <v>7161</v>
+        <v>2808</v>
       </c>
       <c r="D4" t="n">
-        <v>12479</v>
+        <v>8542</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2421</v>
+        <v>690</v>
       </c>
       <c r="C5" t="n">
-        <v>8736</v>
+        <v>4797</v>
       </c>
       <c r="D5" t="n">
-        <v>7092</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1552</v>
+        <v>561</v>
       </c>
       <c r="C6" t="n">
-        <v>8195</v>
+        <v>6094</v>
       </c>
       <c r="D6" t="n">
-        <v>2677</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>523</v>
+        <v>258</v>
       </c>
       <c r="C7" t="n">
-        <v>5463</v>
+        <v>5254</v>
       </c>
       <c r="D7" t="n">
-        <v>914</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>2678</v>
+        <v>2908</v>
       </c>
       <c r="D8" t="n">
-        <v>448</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>956</v>
+        <v>1023</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5049</v>
+        <v>4179</v>
       </c>
       <c r="C2" t="n">
-        <v>4612</v>
+        <v>6535</v>
       </c>
       <c r="D2" t="n">
-        <v>7459</v>
+        <v>7466</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3592</v>
+        <v>737</v>
       </c>
       <c r="C2" t="n">
-        <v>5658</v>
+        <v>9888</v>
       </c>
       <c r="D2" t="n">
-        <v>17862</v>
+        <v>17139</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3258</v>
+        <v>371</v>
       </c>
       <c r="C3" t="n">
-        <v>5978</v>
+        <v>3902</v>
       </c>
       <c r="D3" t="n">
-        <v>15252</v>
+        <v>8004</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3603</v>
+        <v>378</v>
       </c>
       <c r="C4" t="n">
-        <v>10110</v>
+        <v>3052</v>
       </c>
       <c r="D4" t="n">
-        <v>12723</v>
+        <v>8219</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1456</v>
+        <v>557</v>
       </c>
       <c r="C5" t="n">
-        <v>12120</v>
+        <v>3780</v>
       </c>
       <c r="D5" t="n">
-        <v>6444</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>483</v>
+        <v>574</v>
       </c>
       <c r="C6" t="n">
-        <v>6799</v>
+        <v>5462</v>
       </c>
       <c r="D6" t="n">
-        <v>2064</v>
+        <v>2964</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>2624</v>
+        <v>5562</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>936</v>
+        <v>3895</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>1779</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>584</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6600</v>
+        <v>4588</v>
       </c>
       <c r="C2" t="n">
-        <v>4846</v>
+        <v>5294</v>
       </c>
       <c r="D2" t="n">
-        <v>13209</v>
+        <v>11695</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2146</v>
+        <v>1381</v>
       </c>
       <c r="C3" t="n">
-        <v>2361</v>
+        <v>2580</v>
       </c>
       <c r="D3" t="n">
-        <v>1952</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4204</v>
+        <v>3032</v>
       </c>
       <c r="C2" t="n">
-        <v>4062</v>
+        <v>3153</v>
       </c>
       <c r="D2" t="n">
-        <v>18948</v>
+        <v>11529</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3588</v>
+        <v>2523</v>
       </c>
       <c r="C3" t="n">
-        <v>3264</v>
+        <v>3619</v>
       </c>
       <c r="D3" t="n">
-        <v>3699</v>
+        <v>3286</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>966</v>
+        <v>664</v>
       </c>
       <c r="C4" t="n">
-        <v>1449</v>
+        <v>1657</v>
       </c>
       <c r="D4" t="n">
-        <v>1574</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5540</v>
+        <v>2558</v>
       </c>
       <c r="C2" t="n">
-        <v>6048</v>
+        <v>9542</v>
       </c>
       <c r="D2" t="n">
-        <v>30636</v>
+        <v>18371</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3240</v>
+        <v>2295</v>
       </c>
       <c r="C3" t="n">
-        <v>3201</v>
+        <v>2874</v>
       </c>
       <c r="D3" t="n">
-        <v>5872</v>
+        <v>4428</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1925</v>
+        <v>1416</v>
       </c>
       <c r="C4" t="n">
-        <v>2432</v>
+        <v>2809</v>
       </c>
       <c r="D4" t="n">
-        <v>1934</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>457</v>
+        <v>335</v>
       </c>
       <c r="C5" t="n">
-        <v>899</v>
+        <v>1051</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5538</v>
+        <v>2055</v>
       </c>
       <c r="C2" t="n">
-        <v>5947</v>
+        <v>5929</v>
       </c>
       <c r="D2" t="n">
-        <v>34206</v>
+        <v>28252</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3546</v>
+        <v>2001</v>
       </c>
       <c r="C3" t="n">
-        <v>4079</v>
+        <v>5732</v>
       </c>
       <c r="D3" t="n">
-        <v>9222</v>
+        <v>6444</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2183</v>
+        <v>1612</v>
       </c>
       <c r="C4" t="n">
-        <v>2802</v>
+        <v>2788</v>
       </c>
       <c r="D4" t="n">
-        <v>2574</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>990</v>
+        <v>755</v>
       </c>
       <c r="C5" t="n">
-        <v>1689</v>
+        <v>2024</v>
       </c>
       <c r="D5" t="n">
-        <v>1304</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="C6" t="n">
-        <v>599</v>
+        <v>689</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6823</v>
+        <v>3251</v>
       </c>
       <c r="C2" t="n">
-        <v>9483</v>
+        <v>7112</v>
       </c>
       <c r="D2" t="n">
-        <v>36147</v>
+        <v>22565</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3299</v>
+        <v>1675</v>
       </c>
       <c r="C3" t="n">
-        <v>4135</v>
+        <v>5062</v>
       </c>
       <c r="D3" t="n">
-        <v>11637</v>
+        <v>9469</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1789</v>
+        <v>1559</v>
       </c>
       <c r="C4" t="n">
-        <v>2885</v>
+        <v>4369</v>
       </c>
       <c r="D4" t="n">
-        <v>3216</v>
+        <v>2979</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>827</v>
+        <v>1015</v>
       </c>
       <c r="C5" t="n">
-        <v>1652</v>
+        <v>2392</v>
       </c>
       <c r="D5" t="n">
-        <v>1212</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>419</v>
       </c>
       <c r="C6" t="n">
-        <v>781</v>
+        <v>1373</v>
       </c>
       <c r="D6" t="n">
-        <v>761</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>305</v>
+        <v>494</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6379</v>
+        <v>2319</v>
       </c>
       <c r="C2" t="n">
-        <v>7385</v>
+        <v>13757</v>
       </c>
       <c r="D2" t="n">
-        <v>26183</v>
+        <v>26867</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4214</v>
+        <v>1981</v>
       </c>
       <c r="C3" t="n">
-        <v>6284</v>
+        <v>5316</v>
       </c>
       <c r="D3" t="n">
-        <v>15075</v>
+        <v>10883</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2221</v>
+        <v>1386</v>
       </c>
       <c r="C4" t="n">
-        <v>3592</v>
+        <v>4644</v>
       </c>
       <c r="D4" t="n">
-        <v>4896</v>
+        <v>3981</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1174</v>
+        <v>1128</v>
       </c>
       <c r="C5" t="n">
-        <v>2351</v>
+        <v>3348</v>
       </c>
       <c r="D5" t="n">
-        <v>1579</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>524</v>
+        <v>622</v>
       </c>
       <c r="C6" t="n">
-        <v>1273</v>
+        <v>1857</v>
       </c>
       <c r="D6" t="n">
-        <v>829</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="C7" t="n">
-        <v>575</v>
+        <v>911</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>265</v>
+        <v>391</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4564</v>
+        <v>2142</v>
       </c>
       <c r="C2" t="n">
-        <v>5956</v>
+        <v>8254</v>
       </c>
       <c r="D2" t="n">
-        <v>29531</v>
+        <v>20953</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4346</v>
+        <v>2581</v>
       </c>
       <c r="C3" t="n">
-        <v>5957</v>
+        <v>9325</v>
       </c>
       <c r="D3" t="n">
-        <v>15766</v>
+        <v>12058</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>1042</v>
       </c>
       <c r="C4" t="n">
-        <v>5067</v>
+        <v>6201</v>
       </c>
       <c r="D4" t="n">
-        <v>6654</v>
+        <v>3799</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1483</v>
+        <v>574</v>
       </c>
       <c r="C5" t="n">
-        <v>2993</v>
+        <v>1819</v>
       </c>
       <c r="D5" t="n">
-        <v>2167</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>776</v>
+        <v>217</v>
       </c>
       <c r="C6" t="n">
-        <v>1837</v>
+        <v>892</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>94</v>
       </c>
       <c r="C7" t="n">
-        <v>938</v>
+        <v>383</v>
       </c>
       <c r="D7" t="n">
-        <v>597</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>425</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
